--- a/hr_saas_unit_economics.xlsx
+++ b/hr_saas_unit_economics.xlsx
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Assumption within the public India range (per employee per month): Asanify ₹99-199; Keka ₹90-150 per extra employee (third-party report); RazorpayX ₹150 per extra employee; greytHR ₹45-85 and Zoho ₹40-100 per extra employee.</t>
+          <t>Assumption within the public India range (per employee per month): Asanify ₹99-199; Keka ₹90-150 per extra employee (third-party report); RazorpayX ₹150 per extra employee; greytHR ₹45-85 and Zoho ₹40-80 per extra employee (annual billing).</t>
         </is>
       </c>
     </row>
